--- a/ttl_long/AdHoc_Net_5.xlsx
+++ b/ttl_long/AdHoc_Net_5.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,12 +443,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -460,12 +460,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>170</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>97</t>
         </is>
       </c>
     </row>
@@ -477,12 +477,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>374</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>196</t>
         </is>
       </c>
     </row>
@@ -511,12 +511,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>213</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>59</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>378</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>126</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>401</t>
         </is>
       </c>
     </row>
@@ -562,12 +562,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>206</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>361</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>301</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>385</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>449</t>
+          <t>591</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>182</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>437</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>297</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>450</t>
         </is>
       </c>
     </row>
@@ -647,12 +647,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>96</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>680</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>648</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>297</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>683</t>
         </is>
       </c>
     </row>
@@ -698,12 +698,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>781</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>239</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>874</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>278</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>852</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>947</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>93</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>819</t>
+          <t>966</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>361</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>1010</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>1196</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>257</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>985</t>
+          <t>1175</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>1117</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1077</t>
+          <t>1405</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>69</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1082</t>
+          <t>1331</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>305</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1154</t>
+          <t>1336</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>55</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1452</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>64</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1411</t>
+          <t>1418</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>161</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>1514</t>
         </is>
       </c>
     </row>
@@ -953,80 +953,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1478</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1558</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>355</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>1684</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>1508</t>
+          <t>1540</t>
         </is>
       </c>
     </row>
@@ -1041,7 +973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D92"/>
+  <dimension ref="A1:D74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1135,12 +1067,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1162,7 +1094,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1184,7 +1116,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1201,12 +1133,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1245,12 +1177,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1272,7 +1204,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1289,12 +1221,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1311,12 +1243,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1333,12 +1265,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1355,12 +1287,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1377,12 +1309,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1399,12 +1331,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1421,12 +1353,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1443,12 +1375,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1465,12 +1397,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1487,12 +1419,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1509,12 +1441,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1531,12 +1463,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1553,12 +1485,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1575,12 +1507,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1597,12 +1529,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1619,12 +1551,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1641,12 +1573,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1663,12 +1595,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1685,12 +1617,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1707,12 +1639,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1729,7 +1661,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1751,12 +1683,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1773,12 +1705,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1795,12 +1727,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1817,12 +1749,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1839,12 +1771,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1861,12 +1793,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1883,12 +1815,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1905,12 +1837,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1927,12 +1859,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1949,12 +1881,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1971,12 +1903,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1993,7 +1925,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2015,12 +1947,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2037,12 +1969,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2059,12 +1991,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2081,12 +2013,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2103,12 +2035,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2125,12 +2057,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2147,12 +2079,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2169,12 +2101,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2191,12 +2123,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2213,12 +2145,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2235,12 +2167,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2257,12 +2189,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2279,12 +2211,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2301,12 +2233,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2323,12 +2255,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2345,12 +2277,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2367,12 +2299,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2389,12 +2321,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
           <t>21</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>25</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2411,12 +2343,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2433,12 +2365,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2455,12 +2387,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2477,12 +2409,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2499,12 +2431,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2521,12 +2453,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2543,12 +2475,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2565,12 +2497,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2587,12 +2519,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2609,12 +2541,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2631,12 +2563,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2653,7 +2585,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2667,402 +2599,6 @@
         </is>
       </c>
       <c r="D74" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
@@ -3101,7 +2637,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -3111,7 +2647,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
@@ -3137,7 +2673,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>jamm_powe</t>
+          <t>jamm_power</t>
         </is>
       </c>
       <c r="B6" t="n">

--- a/ttl_long/AdHoc_Net_5.xlsx
+++ b/ttl_long/AdHoc_Net_5.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,12 +443,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>46</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>42</t>
         </is>
       </c>
     </row>
@@ -460,12 +460,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>97</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>72</t>
         </is>
       </c>
     </row>
@@ -477,12 +477,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>305</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>87</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>197</t>
         </is>
       </c>
     </row>
@@ -511,12 +511,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>86</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>187</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>302</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>108</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>116</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>205</t>
         </is>
       </c>
     </row>
@@ -562,12 +562,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>243</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>298</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>341</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>241</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>380</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>184</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>438</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>349</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>364</t>
         </is>
       </c>
     </row>
@@ -647,12 +647,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>70</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>505</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>183</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>581</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>280</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>540</t>
         </is>
       </c>
     </row>
@@ -698,12 +698,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>52</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>656</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>272</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>694</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>366</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>647</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>93</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>746</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>239</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>705</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>338</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>752</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>54</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1196</t>
+          <t>897</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>171</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1175</t>
+          <t>876</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>318</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>878</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>89</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1405</t>
+          <t>920</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>171</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1331</t>
+          <t>965</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>359</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1336</t>
+          <t>980</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>48</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1452</t>
+          <t>1154</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>170</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1418</t>
+          <t>1181</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>390</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>1120</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,182 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>80</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1540</t>
+          <t>1164</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1171</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1258</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1454</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1427</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1362</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1470</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1461</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1494</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1606</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1539</t>
         </is>
       </c>
     </row>
@@ -973,7 +1143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D74"/>
+  <dimension ref="A1:D112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1067,12 +1237,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1116,7 +1286,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1133,7 +1303,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1177,12 +1347,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1204,7 +1374,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1221,7 +1391,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1243,12 +1413,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1265,7 +1435,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1287,12 +1457,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1309,12 +1479,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1331,12 +1501,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1353,12 +1523,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1375,12 +1545,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1397,12 +1567,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1419,12 +1589,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1441,12 +1611,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1463,12 +1633,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1485,7 +1655,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1507,12 +1677,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1529,12 +1699,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1551,12 +1721,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1573,7 +1743,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1595,12 +1765,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1617,12 +1787,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1639,12 +1809,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1661,12 +1831,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1683,12 +1853,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1705,12 +1875,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1727,12 +1897,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1749,12 +1919,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1771,12 +1941,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1793,12 +1963,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1815,12 +1985,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1837,12 +2007,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1859,12 +2029,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1881,12 +2051,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1903,12 +2073,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1925,12 +2095,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1947,12 +2117,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1969,12 +2139,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1991,12 +2161,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2013,12 +2183,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2035,12 +2205,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2057,12 +2227,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2079,12 +2249,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2101,12 +2271,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2123,12 +2293,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2145,12 +2315,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2167,12 +2337,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
           <t>22</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>26</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2189,12 +2359,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2211,12 +2381,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2233,7 +2403,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2255,12 +2425,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2277,12 +2447,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2299,12 +2469,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
           <t>24</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>25</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2321,12 +2491,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
           <t>25</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>21</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2343,12 +2513,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2365,12 +2535,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2387,12 +2557,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2409,12 +2579,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2431,12 +2601,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2453,12 +2623,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2475,12 +2645,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2497,12 +2667,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2519,12 +2689,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2541,7 +2711,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2563,12 +2733,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2585,20 +2755,856 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
@@ -2637,7 +3643,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -2647,7 +3653,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
@@ -2667,7 +3673,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>800</v>
+        <v>250</v>
       </c>
     </row>
     <row r="6">

--- a/ttl_long/AdHoc_Net_5.xlsx
+++ b/ttl_long/AdHoc_Net_5.xlsx
@@ -443,12 +443,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -460,12 +460,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>82</t>
         </is>
       </c>
     </row>
@@ -477,12 +477,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>278</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>87</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>197</t>
         </is>
       </c>
     </row>
@@ -511,12 +511,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>230</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>185</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>353</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>135</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>58</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>226</t>
         </is>
       </c>
     </row>
@@ -562,12 +562,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>259</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>245</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>361</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>259</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>113</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>424</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>242</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>397</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>317</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>414</t>
         </is>
       </c>
     </row>
@@ -647,12 +647,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>68</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>529</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>179</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>530</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>373</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>458</t>
         </is>
       </c>
     </row>
@@ -698,12 +698,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>106</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>683</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>262</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>670</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>321</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>641</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>779</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>267</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>731</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>368</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>752</t>
+          <t>703</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>897</t>
+          <t>894</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>121</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>877</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>342</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>855</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>45</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>1046</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>237</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>965</t>
+          <t>992</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>285</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>1029</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>95</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1154</t>
+          <t>1054</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>265</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1181</t>
+          <t>1173</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>298</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1120</t>
+          <t>1116</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>52</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1164</t>
+          <t>1184</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>273</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>1266</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>319</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1258</t>
+          <t>1273</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>41</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1454</t>
+          <t>1447</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>190</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1427</t>
+          <t>1428</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>390</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1362</t>
+          <t>1358</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1470</t>
+          <t>1416</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1461</t>
+          <t>1452</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>305</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1606</t>
+          <t>1653</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>242</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1539</t>
+          <t>1644</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D112"/>
+  <dimension ref="A1:D114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1237,7 +1237,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1369,12 +1369,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1435,7 +1435,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1479,12 +1479,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1523,12 +1523,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1545,12 +1545,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1567,12 +1567,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1589,12 +1589,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1611,7 +1611,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1633,12 +1633,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1655,12 +1655,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1677,12 +1677,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1721,12 +1721,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1743,12 +1743,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1787,12 +1787,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1809,12 +1809,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1831,12 +1831,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1853,7 +1853,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1875,12 +1875,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1897,12 +1897,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1919,12 +1919,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1941,12 +1941,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1963,12 +1963,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2007,12 +2007,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2117,12 +2117,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2139,12 +2139,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2161,12 +2161,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2183,12 +2183,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2205,12 +2205,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2227,12 +2227,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2249,12 +2249,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2315,12 +2315,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2381,12 +2381,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2403,12 +2403,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2447,12 +2447,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2513,12 +2513,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2601,12 +2601,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2623,12 +2623,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2733,12 +2733,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2799,12 +2799,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2865,12 +2865,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2931,12 +2931,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2953,12 +2953,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2997,12 +2997,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3063,12 +3063,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3085,12 +3085,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3129,12 +3129,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3151,12 +3151,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3173,12 +3173,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3195,12 +3195,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3217,12 +3217,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3261,7 +3261,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3283,12 +3283,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3305,12 +3305,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3327,12 +3327,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3349,12 +3349,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3371,12 +3371,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
           <t>35</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>37</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3393,12 +3393,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3415,12 +3415,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3437,12 +3437,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3459,12 +3459,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3481,12 +3481,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3503,12 +3503,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3525,12 +3525,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3547,12 +3547,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3569,12 +3569,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3591,20 +3591,64 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
